--- a/data/trans_orig/P15E_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P15E_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año en 2023</t>
+          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>64,86%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>442</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,16%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>347</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>76,45%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,3%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>12412</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21676</t>
+          <t>21315</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>80,04%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>12699</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>17003</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22043</t>
+          <t>22055</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21199</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27385</t>
+          <t>27418</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,96%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>482</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17278</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24629</t>
+          <t>24653</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17278</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24629</t>
+          <t>24653</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,07%</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>40,2%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>25485</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52329</t>
+          <t>53053</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63820</t>
+          <t>64572</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72916</t>
+          <t>72525</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87222</t>
+          <t>87039</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,2%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>16519</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17167</t>
+          <t>16415</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28658</t>
+          <t>27934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27003</t>
+          <t>27186</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41309</t>
+          <t>41700</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15E_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P15E_R-Clase-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>614</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,27 +1068,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>557</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>85,1%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>6435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>363</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>72,83%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12412</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>19684</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13932</t>
+          <t>15626</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21315</t>
+          <t>23483</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>81,98%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>9809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>13020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19951</t>
+          <t>21100</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17003</t>
+          <t>18269</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>23342</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>25937</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>22035</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27418</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,66%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>499</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>25822</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>25822</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>25822</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>23250</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>19431</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24653</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>23250</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>19431</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24653</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>84,24%</t>
         </is>
       </c>
     </row>
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11931</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11931</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,27 +2783,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21343</t>
+          <t>23596</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>18774</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25485</t>
+          <t>28102</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>58503</t>
+          <t>63586</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53053</t>
+          <t>57248</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64572</t>
+          <t>69519</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>79846</t>
+          <t>87182</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72525</t>
+          <t>78736</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87039</t>
+          <t>94571</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,47%</t>
         </is>
       </c>
     </row>
@@ -2896,22 +2896,22 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16519</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27934</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>34379</t>
+          <t>36486</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27186</t>
+          <t>29097</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41700</t>
+          <t>44932</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>36648</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>36648</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>36648</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>80987</t>
+          <t>87020</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>80987</t>
+          <t>87020</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80987</t>
+          <t>87020</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>114225</t>
+          <t>123668</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>114225</t>
+          <t>123668</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>114225</t>
+          <t>123668</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
